--- a/data/chapter2/FREDv3subset/photosynthetic_pathways.xlsx
+++ b/data/chapter2/FREDv3subset/photosynthetic_pathways.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westernsydneyedu-my.sharepoint.com/personal/90963425_westernsydney_edu_au/Documents/PhD/code/data/chapter2/FREDv3subset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{DDF42CF1-A2FB-4F82-A875-8912E56C72D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EFFDD88-C01E-485B-9A1A-E716F51BE554}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{DDF42CF1-A2FB-4F82-A875-8912E56C72D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B600F0D-594E-427A-A3BD-E5BF28B9119B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{120070BA-0EA9-4896-BF43-310C4A1A1B05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{120070BA-0EA9-4896-BF43-310C4A1A1B05}"/>
   </bookViews>
   <sheets>
     <sheet name="FRED" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5099" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="1004">
   <si>
     <t>F01286</t>
   </si>
@@ -3043,6 +3043,12 @@
   </si>
   <si>
     <t>de la Riva, Navarro-Fernandez, Perez-Ramos, Villar, Maranon. Unpublished.</t>
+  </si>
+  <si>
+    <t>filled_from</t>
+  </si>
+  <si>
+    <t>filled_from_reference</t>
   </si>
 </sst>
 </file>
@@ -3091,7 +3097,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="15">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -3145,17 +3157,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C1F2BDB-3D96-4868-BAB1-40723E973DEF}" name="FRED_subset_collab_categorical" displayName="FRED_subset_collab_categorical" ref="A1:D548" totalsRowShown="0">
-  <autoFilter ref="A1:D548" xr:uid="{5C1F2BDB-3D96-4868-BAB1-40723E973DEF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C1F2BDB-3D96-4868-BAB1-40723E973DEF}" name="FRED_subset_collab_categorical" displayName="FRED_subset_collab_categorical" ref="A1:F548" totalsRowShown="0">
+  <autoFilter ref="A1:F548" xr:uid="{5C1F2BDB-3D96-4868-BAB1-40723E973DEF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D548">
     <sortCondition ref="A2:A548"/>
     <sortCondition ref="B2:B548"/>
   </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{E11980BE-A519-4F77-A22C-3F32A9E43767}" name="F01286" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{8E872ABB-57BD-4F4E-AD5C-F513B8F0BE08}" name="F01287" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{13BF8421-1967-4D9E-B040-CB6CED1615A1}" name="F00043" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{CED1A365-9786-4D61-A6D6-ADB2777A1E8F}" name="F00004" dataDxfId="10"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{E11980BE-A519-4F77-A22C-3F32A9E43767}" name="F01286" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{8E872ABB-57BD-4F4E-AD5C-F513B8F0BE08}" name="F01287" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{13BF8421-1967-4D9E-B040-CB6CED1615A1}" name="F00043" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{CED1A365-9786-4D61-A6D6-ADB2777A1E8F}" name="F00004" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{1D1DD6CA-03A9-4F76-90CE-9652EA58188C}" name="filled_from" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{4CA78F14-C601-433D-8E64-FAD21A3F8D1F}" name="filled_from_reference" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3168,15 +3182,15 @@
     <sortCondition ref="A1:A323"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{89762ECE-5394-4225-88D8-76395507C184}" name="binominal" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{D59F3C61-A62E-4519-932D-63FF695708F7}" name="F00004" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{D56FB15E-7BB5-4548-9827-52A98ED2A0FF}" name="F00043" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{FDB35264-07C2-40E5-9ED1-F900F7A83E10}" name="photosyntheticPathway_combined" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{6A6C7A13-4200-471B-B81E-69BE176EB47D}" name="Dataset" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{2E12852B-7E42-4197-A144-EDDF2E79865D}" name="OrigValueStr" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{1B0F02FD-5867-4600-8AD5-22B9A5912117}" name="photosyntheticPathway" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{ED4FE017-3F2E-41A6-B7E9-35B21C7D6CD0}" name="references" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{0FB33E1C-A96C-4BFC-B148-72CFA2837233}" name="referencesDataset" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{89762ECE-5394-4225-88D8-76395507C184}" name="binominal" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{D59F3C61-A62E-4519-932D-63FF695708F7}" name="F00004" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{D56FB15E-7BB5-4548-9827-52A98ED2A0FF}" name="F00043" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{FDB35264-07C2-40E5-9ED1-F900F7A83E10}" name="photosyntheticPathway_combined" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{6A6C7A13-4200-471B-B81E-69BE176EB47D}" name="Dataset" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{2E12852B-7E42-4197-A144-EDDF2E79865D}" name="OrigValueStr" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{1B0F02FD-5867-4600-8AD5-22B9A5912117}" name="photosyntheticPathway" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{ED4FE017-3F2E-41A6-B7E9-35B21C7D6CD0}" name="references" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{0FB33E1C-A96C-4BFC-B148-72CFA2837233}" name="referencesDataset" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3499,15 +3513,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3B4E9C-159A-42AB-954B-37E8E6AE04B9}">
-  <dimension ref="A1:D548"/>
+  <dimension ref="A1:F548"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="17.5703125" customWidth="1"/>
     <col min="4" max="4" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3520,8 +3536,14 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>455</v>
       </c>
@@ -3534,8 +3556,10 @@
       <c r="D2" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>374</v>
       </c>
@@ -3548,8 +3572,10 @@
       <c r="D3" s="1" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>374</v>
       </c>
@@ -3562,8 +3588,10 @@
       <c r="D4" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>281</v>
       </c>
@@ -3576,8 +3604,10 @@
       <c r="D5" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>281</v>
       </c>
@@ -3590,8 +3620,10 @@
       <c r="D6" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>281</v>
       </c>
@@ -3604,8 +3636,10 @@
       <c r="D7" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>281</v>
       </c>
@@ -3618,8 +3652,10 @@
       <c r="D8" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -3632,8 +3668,10 @@
       <c r="D9" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -3646,8 +3684,10 @@
       <c r="D10" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -3660,8 +3700,10 @@
       <c r="D11" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -3674,8 +3716,10 @@
       <c r="D12" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
@@ -3688,8 +3732,10 @@
       <c r="D13" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>4</v>
       </c>
@@ -3702,8 +3748,10 @@
       <c r="D14" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -3716,8 +3764,10 @@
       <c r="D15" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>4</v>
       </c>
@@ -3730,8 +3780,10 @@
       <c r="D16" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -3744,8 +3796,10 @@
       <c r="D17" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>4</v>
       </c>
@@ -3758,8 +3812,10 @@
       <c r="D18" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>4</v>
       </c>
@@ -3772,8 +3828,10 @@
       <c r="D19" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>4</v>
       </c>
@@ -3786,8 +3844,10 @@
       <c r="D20" s="1" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>4</v>
       </c>
@@ -3800,8 +3860,10 @@
       <c r="D21" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>4</v>
       </c>
@@ -3814,8 +3876,10 @@
       <c r="D22" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -3828,8 +3892,10 @@
       <c r="D23" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
@@ -3842,8 +3908,10 @@
       <c r="D24" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
@@ -3856,8 +3924,10 @@
       <c r="D25" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>4</v>
       </c>
@@ -3870,8 +3940,10 @@
       <c r="D26" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>4</v>
       </c>
@@ -3884,8 +3956,10 @@
       <c r="D27" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>4</v>
       </c>
@@ -3898,8 +3972,10 @@
       <c r="D28" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>4</v>
       </c>
@@ -3912,8 +3988,10 @@
       <c r="D29" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>4</v>
       </c>
@@ -3926,8 +4004,10 @@
       <c r="D30" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>4</v>
       </c>
@@ -3940,8 +4020,10 @@
       <c r="D31" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
@@ -3954,8 +4036,10 @@
       <c r="D32" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
@@ -3968,8 +4052,10 @@
       <c r="D33" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
@@ -3982,8 +4068,10 @@
       <c r="D34" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
@@ -3996,8 +4084,10 @@
       <c r="D35" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>231</v>
       </c>
@@ -4010,8 +4100,10 @@
       <c r="D36" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>231</v>
       </c>
@@ -4024,8 +4116,10 @@
       <c r="D37" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>554</v>
       </c>
@@ -4038,8 +4132,10 @@
       <c r="D38" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>523</v>
       </c>
@@ -4052,8 +4148,10 @@
       <c r="D39" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>575</v>
       </c>
@@ -4066,8 +4164,10 @@
       <c r="D40" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>294</v>
       </c>
@@ -4080,8 +4180,10 @@
       <c r="D41" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>294</v>
       </c>
@@ -4094,8 +4196,10 @@
       <c r="D42" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>589</v>
       </c>
@@ -4108,8 +4212,10 @@
       <c r="D43" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>93</v>
       </c>
@@ -4122,8 +4228,10 @@
       <c r="D44" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>93</v>
       </c>
@@ -4136,8 +4244,10 @@
       <c r="D45" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>93</v>
       </c>
@@ -4150,8 +4260,10 @@
       <c r="D46" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>93</v>
       </c>
@@ -4164,8 +4276,10 @@
       <c r="D47" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>459</v>
       </c>
@@ -4178,8 +4292,10 @@
       <c r="D48" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>329</v>
       </c>
@@ -4192,8 +4308,10 @@
       <c r="D49" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>290</v>
       </c>
@@ -4206,8 +4324,10 @@
       <c r="D50" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>344</v>
       </c>
@@ -4220,8 +4340,10 @@
       <c r="D51" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>344</v>
       </c>
@@ -4234,8 +4356,10 @@
       <c r="D52" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>237</v>
       </c>
@@ -4248,8 +4372,10 @@
       <c r="D53" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>148</v>
       </c>
@@ -4262,8 +4388,10 @@
       <c r="D54" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>148</v>
       </c>
@@ -4276,8 +4404,10 @@
       <c r="D55" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>148</v>
       </c>
@@ -4290,8 +4420,10 @@
       <c r="D56" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>43</v>
       </c>
@@ -4304,8 +4436,10 @@
       <c r="D57" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>43</v>
       </c>
@@ -4318,8 +4452,10 @@
       <c r="D58" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>43</v>
       </c>
@@ -4332,8 +4468,10 @@
       <c r="D59" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>509</v>
       </c>
@@ -4346,8 +4484,10 @@
       <c r="D60" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>246</v>
       </c>
@@ -4360,8 +4500,10 @@
       <c r="D61" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
@@ -4374,8 +4516,10 @@
       <c r="D62" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>68</v>
       </c>
@@ -4388,8 +4532,10 @@
       <c r="D63" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>557</v>
       </c>
@@ -4402,8 +4548,10 @@
       <c r="D64" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>557</v>
       </c>
@@ -4416,8 +4564,10 @@
       <c r="D65" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>215</v>
       </c>
@@ -4430,8 +4580,10 @@
       <c r="D66" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>364</v>
       </c>
@@ -4444,8 +4596,10 @@
       <c r="D67" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>211</v>
       </c>
@@ -4458,8 +4612,10 @@
       <c r="D68" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>211</v>
       </c>
@@ -4472,8 +4628,10 @@
       <c r="D69" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>211</v>
       </c>
@@ -4486,8 +4644,10 @@
       <c r="D70" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>279</v>
       </c>
@@ -4500,8 +4660,10 @@
       <c r="D71" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>279</v>
       </c>
@@ -4514,8 +4676,10 @@
       <c r="D72" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>160</v>
       </c>
@@ -4528,8 +4692,10 @@
       <c r="D73" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>160</v>
       </c>
@@ -4542,8 +4708,10 @@
       <c r="D74" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>160</v>
       </c>
@@ -4556,8 +4724,10 @@
       <c r="D75" s="1" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>391</v>
       </c>
@@ -4570,8 +4740,10 @@
       <c r="D76" s="1" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>391</v>
       </c>
@@ -4584,8 +4756,10 @@
       <c r="D77" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>391</v>
       </c>
@@ -4598,8 +4772,10 @@
       <c r="D78" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>222</v>
       </c>
@@ -4612,8 +4788,10 @@
       <c r="D79" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>96</v>
       </c>
@@ -4626,8 +4804,10 @@
       <c r="D80" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>96</v>
       </c>
@@ -4640,8 +4820,10 @@
       <c r="D81" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>457</v>
       </c>
@@ -4654,8 +4836,10 @@
       <c r="D82" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>466</v>
       </c>
@@ -4668,8 +4852,10 @@
       <c r="D83" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>463</v>
       </c>
@@ -4682,8 +4868,10 @@
       <c r="D84" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>463</v>
       </c>
@@ -4696,8 +4884,10 @@
       <c r="D85" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>297</v>
       </c>
@@ -4710,8 +4900,10 @@
       <c r="D86" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>297</v>
       </c>
@@ -4724,8 +4916,10 @@
       <c r="D87" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>297</v>
       </c>
@@ -4738,8 +4932,10 @@
       <c r="D88" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>240</v>
       </c>
@@ -4752,8 +4948,10 @@
       <c r="D89" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>240</v>
       </c>
@@ -4766,8 +4964,10 @@
       <c r="D90" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>45</v>
       </c>
@@ -4780,8 +4980,10 @@
       <c r="D91" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>45</v>
       </c>
@@ -4794,8 +4996,10 @@
       <c r="D92" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>45</v>
       </c>
@@ -4808,8 +5012,10 @@
       <c r="D93" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>45</v>
       </c>
@@ -4822,8 +5028,10 @@
       <c r="D94" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>45</v>
       </c>
@@ -4836,8 +5044,10 @@
       <c r="D95" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>45</v>
       </c>
@@ -4850,8 +5060,10 @@
       <c r="D96" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>45</v>
       </c>
@@ -4864,8 +5076,10 @@
       <c r="D97" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>45</v>
       </c>
@@ -4878,8 +5092,10 @@
       <c r="D98" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>45</v>
       </c>
@@ -4892,8 +5108,10 @@
       <c r="D99" s="1" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>421</v>
       </c>
@@ -4906,8 +5124,10 @@
       <c r="D100" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>421</v>
       </c>
@@ -4920,8 +5140,10 @@
       <c r="D101" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>433</v>
       </c>
@@ -4934,8 +5156,10 @@
       <c r="D102" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>426</v>
       </c>
@@ -4948,8 +5172,10 @@
       <c r="D103" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>526</v>
       </c>
@@ -4962,8 +5188,10 @@
       <c r="D104" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>228</v>
       </c>
@@ -4976,8 +5204,10 @@
       <c r="D105" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>228</v>
       </c>
@@ -4990,8 +5220,10 @@
       <c r="D106" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>393</v>
       </c>
@@ -5004,8 +5236,10 @@
       <c r="D107" s="1" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>288</v>
       </c>
@@ -5018,8 +5252,10 @@
       <c r="D108" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>89</v>
       </c>
@@ -5032,8 +5268,10 @@
       <c r="D109" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>89</v>
       </c>
@@ -5046,8 +5284,10 @@
       <c r="D110" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>382</v>
       </c>
@@ -5060,8 +5300,10 @@
       <c r="D111" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>437</v>
       </c>
@@ -5074,8 +5316,10 @@
       <c r="D112" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>202</v>
       </c>
@@ -5088,8 +5332,10 @@
       <c r="D113" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>66</v>
       </c>
@@ -5102,8 +5348,10 @@
       <c r="D114" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>66</v>
       </c>
@@ -5116,8 +5364,10 @@
       <c r="D115" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>66</v>
       </c>
@@ -5130,8 +5380,10 @@
       <c r="D116" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>66</v>
       </c>
@@ -5144,8 +5396,10 @@
       <c r="D117" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>66</v>
       </c>
@@ -5158,8 +5412,10 @@
       <c r="D118" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>66</v>
       </c>
@@ -5172,8 +5428,10 @@
       <c r="D119" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>66</v>
       </c>
@@ -5186,8 +5444,10 @@
       <c r="D120" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>66</v>
       </c>
@@ -5200,8 +5460,10 @@
       <c r="D121" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>66</v>
       </c>
@@ -5214,8 +5476,10 @@
       <c r="D122" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>66</v>
       </c>
@@ -5228,8 +5492,10 @@
       <c r="D123" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>66</v>
       </c>
@@ -5242,8 +5508,10 @@
       <c r="D124" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E124" s="1"/>
+      <c r="F124" s="1"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>66</v>
       </c>
@@ -5256,8 +5524,10 @@
       <c r="D125" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>98</v>
       </c>
@@ -5270,8 +5540,10 @@
       <c r="D126" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>98</v>
       </c>
@@ -5284,8 +5556,10 @@
       <c r="D127" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E127" s="1"/>
+      <c r="F127" s="1"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>248</v>
       </c>
@@ -5298,8 +5572,10 @@
       <c r="D128" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>581</v>
       </c>
@@ -5312,8 +5588,10 @@
       <c r="D129" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>226</v>
       </c>
@@ -5326,8 +5604,10 @@
       <c r="D130" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E130" s="1"/>
+      <c r="F130" s="1"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>100</v>
       </c>
@@ -5340,8 +5620,10 @@
       <c r="D131" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>100</v>
       </c>
@@ -5354,8 +5636,10 @@
       <c r="D132" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E132" s="1"/>
+      <c r="F132" s="1"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>400</v>
       </c>
@@ -5368,8 +5652,10 @@
       <c r="D133" s="1" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E133" s="1"/>
+      <c r="F133" s="1"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>311</v>
       </c>
@@ -5382,8 +5668,10 @@
       <c r="D134" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E134" s="1"/>
+      <c r="F134" s="1"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>102</v>
       </c>
@@ -5396,8 +5684,10 @@
       <c r="D135" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E135" s="1"/>
+      <c r="F135" s="1"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>102</v>
       </c>
@@ -5410,8 +5700,10 @@
       <c r="D136" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>497</v>
       </c>
@@ -5424,8 +5716,10 @@
       <c r="D137" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E137" s="1"/>
+      <c r="F137" s="1"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>144</v>
       </c>
@@ -5438,8 +5732,10 @@
       <c r="D138" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E138" s="1"/>
+      <c r="F138" s="1"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>144</v>
       </c>
@@ -5452,8 +5748,10 @@
       <c r="D139" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E139" s="1"/>
+      <c r="F139" s="1"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>428</v>
       </c>
@@ -5466,8 +5764,10 @@
       <c r="D140" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E140" s="1"/>
+      <c r="F140" s="1"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>60</v>
       </c>
@@ -5480,8 +5780,10 @@
       <c r="D141" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E141" s="1"/>
+      <c r="F141" s="1"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>60</v>
       </c>
@@ -5494,8 +5796,10 @@
       <c r="D142" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E142" s="1"/>
+      <c r="F142" s="1"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>60</v>
       </c>
@@ -5508,8 +5812,10 @@
       <c r="D143" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E143" s="1"/>
+      <c r="F143" s="1"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>60</v>
       </c>
@@ -5522,8 +5828,10 @@
       <c r="D144" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E144" s="1"/>
+      <c r="F144" s="1"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>60</v>
       </c>
@@ -5536,8 +5844,10 @@
       <c r="D145" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E145" s="1"/>
+      <c r="F145" s="1"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>60</v>
       </c>
@@ -5550,8 +5860,10 @@
       <c r="D146" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E146" s="1"/>
+      <c r="F146" s="1"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>60</v>
       </c>
@@ -5564,8 +5876,10 @@
       <c r="D147" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E147" s="1"/>
+      <c r="F147" s="1"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>60</v>
       </c>
@@ -5578,8 +5892,10 @@
       <c r="D148" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E148" s="1"/>
+      <c r="F148" s="1"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>60</v>
       </c>
@@ -5592,8 +5908,10 @@
       <c r="D149" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E149" s="1"/>
+      <c r="F149" s="1"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>60</v>
       </c>
@@ -5606,8 +5924,10 @@
       <c r="D150" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E150" s="1"/>
+      <c r="F150" s="1"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>60</v>
       </c>
@@ -5620,8 +5940,10 @@
       <c r="D151" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E151" s="1"/>
+      <c r="F151" s="1"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>60</v>
       </c>
@@ -5634,8 +5956,10 @@
       <c r="D152" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E152" s="1"/>
+      <c r="F152" s="1"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>453</v>
       </c>
@@ -5648,8 +5972,10 @@
       <c r="D153" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E153" s="1"/>
+      <c r="F153" s="1"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>545</v>
       </c>
@@ -5662,8 +5988,10 @@
       <c r="D154" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E154" s="1"/>
+      <c r="F154" s="1"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>104</v>
       </c>
@@ -5676,8 +6004,10 @@
       <c r="D155" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E155" s="1"/>
+      <c r="F155" s="1"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>104</v>
       </c>
@@ -5690,8 +6020,10 @@
       <c r="D156" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E156" s="1"/>
+      <c r="F156" s="1"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>104</v>
       </c>
@@ -5704,8 +6036,10 @@
       <c r="D157" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E157" s="1"/>
+      <c r="F157" s="1"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>104</v>
       </c>
@@ -5718,8 +6052,10 @@
       <c r="D158" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E158" s="1"/>
+      <c r="F158" s="1"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>104</v>
       </c>
@@ -5732,8 +6068,10 @@
       <c r="D159" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E159" s="1"/>
+      <c r="F159" s="1"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>104</v>
       </c>
@@ -5746,8 +6084,10 @@
       <c r="D160" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>104</v>
       </c>
@@ -5760,8 +6100,10 @@
       <c r="D161" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>104</v>
       </c>
@@ -5774,8 +6116,10 @@
       <c r="D162" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E162" s="1"/>
+      <c r="F162" s="1"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>464</v>
       </c>
@@ -5788,8 +6132,10 @@
       <c r="D163" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E163" s="1"/>
+      <c r="F163" s="1"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>464</v>
       </c>
@@ -5802,8 +6148,10 @@
       <c r="D164" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E164" s="1"/>
+      <c r="F164" s="1"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>559</v>
       </c>
@@ -5816,8 +6164,10 @@
       <c r="D165" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E165" s="1"/>
+      <c r="F165" s="1"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>559</v>
       </c>
@@ -5830,8 +6180,10 @@
       <c r="D166" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E166" s="1"/>
+      <c r="F166" s="1"/>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>559</v>
       </c>
@@ -5844,8 +6196,10 @@
       <c r="D167" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E167" s="1"/>
+      <c r="F167" s="1"/>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>586</v>
       </c>
@@ -5858,8 +6212,10 @@
       <c r="D168" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E168" s="1"/>
+      <c r="F168" s="1"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>272</v>
       </c>
@@ -5872,8 +6228,10 @@
       <c r="D169" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E169" s="1"/>
+      <c r="F169" s="1"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>76</v>
       </c>
@@ -5886,8 +6244,10 @@
       <c r="D170" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E170" s="1"/>
+      <c r="F170" s="1"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>76</v>
       </c>
@@ -5900,8 +6260,10 @@
       <c r="D171" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E171" s="1"/>
+      <c r="F171" s="1"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>76</v>
       </c>
@@ -5914,8 +6276,10 @@
       <c r="D172" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E172" s="1"/>
+      <c r="F172" s="1"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>76</v>
       </c>
@@ -5928,8 +6292,10 @@
       <c r="D173" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E173" s="1"/>
+      <c r="F173" s="1"/>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>76</v>
       </c>
@@ -5942,8 +6308,10 @@
       <c r="D174" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E174" s="1"/>
+      <c r="F174" s="1"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>76</v>
       </c>
@@ -5956,8 +6324,10 @@
       <c r="D175" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E175" s="1"/>
+      <c r="F175" s="1"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>503</v>
       </c>
@@ -5970,8 +6340,10 @@
       <c r="D176" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E176" s="1"/>
+      <c r="F176" s="1"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>157</v>
       </c>
@@ -5984,8 +6356,10 @@
       <c r="D177" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E177" s="1"/>
+      <c r="F177" s="1"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>157</v>
       </c>
@@ -5998,8 +6372,10 @@
       <c r="D178" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E178" s="1"/>
+      <c r="F178" s="1"/>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>157</v>
       </c>
@@ -6012,8 +6388,10 @@
       <c r="D179" s="1" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E179" s="1"/>
+      <c r="F179" s="1"/>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>157</v>
       </c>
@@ -6026,8 +6404,10 @@
       <c r="D180" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E180" s="1"/>
+      <c r="F180" s="1"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>396</v>
       </c>
@@ -6040,8 +6420,10 @@
       <c r="D181" s="1" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E181" s="1"/>
+      <c r="F181" s="1"/>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>300</v>
       </c>
@@ -6054,8 +6436,10 @@
       <c r="D182" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E182" s="1"/>
+      <c r="F182" s="1"/>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>354</v>
       </c>
@@ -6068,8 +6452,10 @@
       <c r="D183" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E183" s="1"/>
+      <c r="F183" s="1"/>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>493</v>
       </c>
@@ -6082,8 +6468,10 @@
       <c r="D184" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E184" s="1"/>
+      <c r="F184" s="1"/>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>292</v>
       </c>
@@ -6096,8 +6484,10 @@
       <c r="D185" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E185" s="1"/>
+      <c r="F185" s="1"/>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>516</v>
       </c>
@@ -6110,8 +6500,10 @@
       <c r="D186" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E186" s="1"/>
+      <c r="F186" s="1"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>443</v>
       </c>
@@ -6124,8 +6516,10 @@
       <c r="D187" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E187" s="1"/>
+      <c r="F187" s="1"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>443</v>
       </c>
@@ -6138,8 +6532,10 @@
       <c r="D188" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E188" s="1"/>
+      <c r="F188" s="1"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>371</v>
       </c>
@@ -6152,8 +6548,10 @@
       <c r="D189" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E189" s="1"/>
+      <c r="F189" s="1"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>371</v>
       </c>
@@ -6166,8 +6564,10 @@
       <c r="D190" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E190" s="1"/>
+      <c r="F190" s="1"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>572</v>
       </c>
@@ -6180,8 +6580,10 @@
       <c r="D191" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E191" s="1"/>
+      <c r="F191" s="1"/>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>106</v>
       </c>
@@ -6194,8 +6596,10 @@
       <c r="D192" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E192" s="1"/>
+      <c r="F192" s="1"/>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>106</v>
       </c>
@@ -6208,8 +6612,10 @@
       <c r="D193" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E193" s="1"/>
+      <c r="F193" s="1"/>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>106</v>
       </c>
@@ -6222,8 +6628,10 @@
       <c r="D194" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E194" s="1"/>
+      <c r="F194" s="1"/>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>488</v>
       </c>
@@ -6236,8 +6644,10 @@
       <c r="D195" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E195" s="1"/>
+      <c r="F195" s="1"/>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>446</v>
       </c>
@@ -6250,8 +6660,10 @@
       <c r="D196" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E196" s="1"/>
+      <c r="F196" s="1"/>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>498</v>
       </c>
@@ -6264,8 +6676,10 @@
       <c r="D197" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E197" s="1"/>
+      <c r="F197" s="1"/>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>498</v>
       </c>
@@ -6278,8 +6692,10 @@
       <c r="D198" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E198" s="1"/>
+      <c r="F198" s="1"/>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>588</v>
       </c>
@@ -6292,8 +6708,10 @@
       <c r="D199" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E199" s="1"/>
+      <c r="F199" s="1"/>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>366</v>
       </c>
@@ -6306,8 +6724,10 @@
       <c r="D200" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E200" s="1"/>
+      <c r="F200" s="1"/>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>78</v>
       </c>
@@ -6320,8 +6740,10 @@
       <c r="D201" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E201" s="1"/>
+      <c r="F201" s="1"/>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>78</v>
       </c>
@@ -6334,8 +6756,10 @@
       <c r="D202" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E202" s="1"/>
+      <c r="F202" s="1"/>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>78</v>
       </c>
@@ -6348,8 +6772,10 @@
       <c r="D203" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E203" s="1"/>
+      <c r="F203" s="1"/>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>78</v>
       </c>
@@ -6362,8 +6788,10 @@
       <c r="D204" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E204" s="1"/>
+      <c r="F204" s="1"/>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>78</v>
       </c>
@@ -6376,8 +6804,10 @@
       <c r="D205" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E205" s="1"/>
+      <c r="F205" s="1"/>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>441</v>
       </c>
@@ -6390,8 +6820,10 @@
       <c r="D206" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E206" s="1"/>
+      <c r="F206" s="1"/>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>511</v>
       </c>
@@ -6404,8 +6836,10 @@
       <c r="D207" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E207" s="1"/>
+      <c r="F207" s="1"/>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>80</v>
       </c>
@@ -6418,8 +6852,10 @@
       <c r="D208" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E208" s="1"/>
+      <c r="F208" s="1"/>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>80</v>
       </c>
@@ -6432,8 +6868,10 @@
       <c r="D209" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E209" s="1"/>
+      <c r="F209" s="1"/>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>80</v>
       </c>
@@ -6446,8 +6884,10 @@
       <c r="D210" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E210" s="1"/>
+      <c r="F210" s="1"/>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>217</v>
       </c>
@@ -6460,8 +6900,10 @@
       <c r="D211" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E211" s="1"/>
+      <c r="F211" s="1"/>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>217</v>
       </c>
@@ -6474,8 +6916,10 @@
       <c r="D212" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E212" s="1"/>
+      <c r="F212" s="1"/>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>302</v>
       </c>
@@ -6488,8 +6932,10 @@
       <c r="D213" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E213" s="1"/>
+      <c r="F213" s="1"/>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>302</v>
       </c>
@@ -6502,8 +6948,10 @@
       <c r="D214" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E214" s="1"/>
+      <c r="F214" s="1"/>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>275</v>
       </c>
@@ -6516,8 +6964,10 @@
       <c r="D215" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E215" s="1"/>
+      <c r="F215" s="1"/>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>197</v>
       </c>
@@ -6530,8 +6980,10 @@
       <c r="D216" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E216" s="1"/>
+      <c r="F216" s="1"/>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>27</v>
       </c>
@@ -6544,8 +6996,10 @@
       <c r="D217" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E217" s="1"/>
+      <c r="F217" s="1"/>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>27</v>
       </c>
@@ -6558,8 +7012,10 @@
       <c r="D218" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E218" s="1"/>
+      <c r="F218" s="1"/>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>27</v>
       </c>
@@ -6572,8 +7028,10 @@
       <c r="D219" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E219" s="1"/>
+      <c r="F219" s="1"/>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>27</v>
       </c>
@@ -6586,8 +7044,10 @@
       <c r="D220" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E220" s="1"/>
+      <c r="F220" s="1"/>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>27</v>
       </c>
@@ -6600,8 +7060,10 @@
       <c r="D221" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E221" s="1"/>
+      <c r="F221" s="1"/>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>543</v>
       </c>
@@ -6614,8 +7076,10 @@
       <c r="D222" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E222" s="1"/>
+      <c r="F222" s="1"/>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>319</v>
       </c>
@@ -6628,8 +7092,10 @@
       <c r="D223" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E223" s="1"/>
+      <c r="F223" s="1"/>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>549</v>
       </c>
@@ -6642,8 +7108,10 @@
       <c r="D224" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E224" s="1"/>
+      <c r="F224" s="1"/>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>220</v>
       </c>
@@ -6656,8 +7124,10 @@
       <c r="D225" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E225" s="1"/>
+      <c r="F225" s="1"/>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>527</v>
       </c>
@@ -6670,8 +7140,10 @@
       <c r="D226" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E226" s="1"/>
+      <c r="F226" s="1"/>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>8</v>
       </c>
@@ -6684,8 +7156,10 @@
       <c r="D227" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E227" s="1"/>
+      <c r="F227" s="1"/>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>8</v>
       </c>
@@ -6698,8 +7172,10 @@
       <c r="D228" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E228" s="1"/>
+      <c r="F228" s="1"/>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>8</v>
       </c>
@@ -6712,8 +7188,10 @@
       <c r="D229" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E229" s="1"/>
+      <c r="F229" s="1"/>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>8</v>
       </c>
@@ -6726,8 +7204,10 @@
       <c r="D230" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E230" s="1"/>
+      <c r="F230" s="1"/>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>8</v>
       </c>
@@ -6740,8 +7220,10 @@
       <c r="D231" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E231" s="1"/>
+      <c r="F231" s="1"/>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>8</v>
       </c>
@@ -6754,8 +7236,10 @@
       <c r="D232" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E232" s="1"/>
+      <c r="F232" s="1"/>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>8</v>
       </c>
@@ -6768,8 +7252,10 @@
       <c r="D233" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E233" s="1"/>
+      <c r="F233" s="1"/>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>8</v>
       </c>
@@ -6782,8 +7268,10 @@
       <c r="D234" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E234" s="1"/>
+      <c r="F234" s="1"/>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>8</v>
       </c>
@@ -6796,8 +7284,10 @@
       <c r="D235" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E235" s="1"/>
+      <c r="F235" s="1"/>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>8</v>
       </c>
@@ -6810,8 +7300,10 @@
       <c r="D236" s="1" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E236" s="1"/>
+      <c r="F236" s="1"/>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>8</v>
       </c>
@@ -6824,8 +7316,10 @@
       <c r="D237" s="1" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E237" s="1"/>
+      <c r="F237" s="1"/>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>8</v>
       </c>
@@ -6838,8 +7332,10 @@
       <c r="D238" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E238" s="1"/>
+      <c r="F238" s="1"/>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>8</v>
       </c>
@@ -6852,8 +7348,10 @@
       <c r="D239" s="1" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E239" s="1"/>
+      <c r="F239" s="1"/>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>476</v>
       </c>
@@ -6866,8 +7364,10 @@
       <c r="D240" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E240" s="1"/>
+      <c r="F240" s="1"/>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>270</v>
       </c>
@@ -6880,8 +7380,10 @@
       <c r="D241" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E241" s="1"/>
+      <c r="F241" s="1"/>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>270</v>
       </c>
@@ -6894,8 +7396,10 @@
       <c r="D242" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E242" s="1"/>
+      <c r="F242" s="1"/>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>331</v>
       </c>
@@ -6908,8 +7412,10 @@
       <c r="D243" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E243" s="1"/>
+      <c r="F243" s="1"/>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>224</v>
       </c>
@@ -6922,8 +7428,10 @@
       <c r="D244" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E244" s="1"/>
+      <c r="F244" s="1"/>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>108</v>
       </c>
@@ -6936,8 +7444,10 @@
       <c r="D245" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E245" s="1"/>
+      <c r="F245" s="1"/>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>108</v>
       </c>
@@ -6950,8 +7460,10 @@
       <c r="D246" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E246" s="1"/>
+      <c r="F246" s="1"/>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>337</v>
       </c>
@@ -6964,8 +7476,10 @@
       <c r="D247" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E247" s="1"/>
+      <c r="F247" s="1"/>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>244</v>
       </c>
@@ -6978,8 +7492,10 @@
       <c r="D248" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E248" s="1"/>
+      <c r="F248" s="1"/>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>244</v>
       </c>
@@ -6992,8 +7508,10 @@
       <c r="D249" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E249" s="1"/>
+      <c r="F249" s="1"/>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>110</v>
       </c>
@@ -7006,8 +7524,10 @@
       <c r="D250" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E250" s="1"/>
+      <c r="F250" s="1"/>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>110</v>
       </c>
@@ -7020,8 +7540,10 @@
       <c r="D251" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E251" s="1"/>
+      <c r="F251" s="1"/>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>112</v>
       </c>
@@ -7034,8 +7556,10 @@
       <c r="D252" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E252" s="1"/>
+      <c r="F252" s="1"/>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>112</v>
       </c>
@@ -7048,8 +7572,10 @@
       <c r="D253" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E253" s="1"/>
+      <c r="F253" s="1"/>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>193</v>
       </c>
@@ -7062,8 +7588,10 @@
       <c r="D254" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E254" s="1"/>
+      <c r="F254" s="1"/>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>567</v>
       </c>
@@ -7076,8 +7604,10 @@
       <c r="D255" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E255" s="1"/>
+      <c r="F255" s="1"/>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>12</v>
       </c>
@@ -7090,8 +7620,10 @@
       <c r="D256" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E256" s="1"/>
+      <c r="F256" s="1"/>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>113</v>
       </c>
@@ -7104,8 +7636,10 @@
       <c r="D257" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E257" s="1"/>
+      <c r="F257" s="1"/>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>113</v>
       </c>
@@ -7118,8 +7652,10 @@
       <c r="D258" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E258" s="1"/>
+      <c r="F258" s="1"/>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>492</v>
       </c>
@@ -7132,8 +7668,10 @@
       <c r="D259" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E259" s="1"/>
+      <c r="F259" s="1"/>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>269</v>
       </c>
@@ -7146,8 +7684,10 @@
       <c r="D260" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E260" s="1"/>
+      <c r="F260" s="1"/>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>31</v>
       </c>
@@ -7160,8 +7700,10 @@
       <c r="D261" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E261" s="1"/>
+      <c r="F261" s="1"/>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>31</v>
       </c>
@@ -7174,8 +7716,10 @@
       <c r="D262" s="1" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E262" s="1"/>
+      <c r="F262" s="1"/>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>31</v>
       </c>
@@ -7188,8 +7732,10 @@
       <c r="D263" s="1" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E263" s="1"/>
+      <c r="F263" s="1"/>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>31</v>
       </c>
@@ -7202,8 +7748,10 @@
       <c r="D264" s="1" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E264" s="1"/>
+      <c r="F264" s="1"/>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>31</v>
       </c>
@@ -7216,8 +7764,10 @@
       <c r="D265" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E265" s="1"/>
+      <c r="F265" s="1"/>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>31</v>
       </c>
@@ -7230,8 +7780,10 @@
       <c r="D266" s="1" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E266" s="1"/>
+      <c r="F266" s="1"/>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>31</v>
       </c>
@@ -7244,8 +7796,10 @@
       <c r="D267" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E267" s="1"/>
+      <c r="F267" s="1"/>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>31</v>
       </c>
@@ -7258,8 +7812,10 @@
       <c r="D268" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E268" s="1"/>
+      <c r="F268" s="1"/>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>31</v>
       </c>
@@ -7272,8 +7828,10 @@
       <c r="D269" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E269" s="1"/>
+      <c r="F269" s="1"/>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>409</v>
       </c>
@@ -7286,8 +7844,10 @@
       <c r="D270" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E270" s="1"/>
+      <c r="F270" s="1"/>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>409</v>
       </c>
@@ -7300,8 +7860,10 @@
       <c r="D271" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E271" s="1"/>
+      <c r="F271" s="1"/>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>340</v>
       </c>
@@ -7314,8 +7876,10 @@
       <c r="D272" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E272" s="1"/>
+      <c r="F272" s="1"/>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>116</v>
       </c>
@@ -7328,8 +7892,10 @@
       <c r="D273" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E273" s="1"/>
+      <c r="F273" s="1"/>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>116</v>
       </c>
@@ -7342,8 +7908,10 @@
       <c r="D274" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E274" s="1"/>
+      <c r="F274" s="1"/>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>593</v>
       </c>
@@ -7356,8 +7924,10 @@
       <c r="D275" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E275" s="1"/>
+      <c r="F275" s="1"/>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>14</v>
       </c>
@@ -7370,8 +7940,10 @@
       <c r="D276" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E276" s="1"/>
+      <c r="F276" s="1"/>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>14</v>
       </c>
@@ -7384,8 +7956,10 @@
       <c r="D277" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E277" s="1"/>
+      <c r="F277" s="1"/>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>14</v>
       </c>
@@ -7398,8 +7972,10 @@
       <c r="D278" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E278" s="1"/>
+      <c r="F278" s="1"/>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>14</v>
       </c>
@@ -7412,8 +7988,10 @@
       <c r="D279" s="1" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E279" s="1"/>
+      <c r="F279" s="1"/>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>14</v>
       </c>
@@ -7426,8 +8004,10 @@
       <c r="D280" s="1" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E280" s="1"/>
+      <c r="F280" s="1"/>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>14</v>
       </c>
@@ -7440,8 +8020,10 @@
       <c r="D281" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E281" s="1"/>
+      <c r="F281" s="1"/>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>14</v>
       </c>
@@ -7454,8 +8036,10 @@
       <c r="D282" s="1" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E282" s="1"/>
+      <c r="F282" s="1"/>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>448</v>
       </c>
@@ -7468,8 +8052,10 @@
       <c r="D283" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E283" s="1"/>
+      <c r="F283" s="1"/>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>448</v>
       </c>
@@ -7482,8 +8068,10 @@
       <c r="D284" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E284" s="1"/>
+      <c r="F284" s="1"/>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>335</v>
       </c>
@@ -7496,8 +8084,10 @@
       <c r="D285" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E285" s="1"/>
+      <c r="F285" s="1"/>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>335</v>
       </c>
@@ -7510,8 +8100,10 @@
       <c r="D286" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E286" s="1"/>
+      <c r="F286" s="1"/>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>118</v>
       </c>
@@ -7524,8 +8116,10 @@
       <c r="D287" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E287" s="1"/>
+      <c r="F287" s="1"/>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>118</v>
       </c>
@@ -7538,8 +8132,10 @@
       <c r="D288" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E288" s="1"/>
+      <c r="F288" s="1"/>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>118</v>
       </c>
@@ -7552,8 +8148,10 @@
       <c r="D289" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E289" s="1"/>
+      <c r="F289" s="1"/>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>118</v>
       </c>
@@ -7566,8 +8164,10 @@
       <c r="D290" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E290" s="1"/>
+      <c r="F290" s="1"/>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>120</v>
       </c>
@@ -7580,8 +8180,10 @@
       <c r="D291" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E291" s="1"/>
+      <c r="F291" s="1"/>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>120</v>
       </c>
@@ -7594,8 +8196,10 @@
       <c r="D292" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E292" s="1"/>
+      <c r="F292" s="1"/>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>120</v>
       </c>
@@ -7608,8 +8212,10 @@
       <c r="D293" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E293" s="1"/>
+      <c r="F293" s="1"/>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>120</v>
       </c>
@@ -7622,8 +8228,10 @@
       <c r="D294" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E294" s="1"/>
+      <c r="F294" s="1"/>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>120</v>
       </c>
@@ -7636,8 +8244,10 @@
       <c r="D295" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E295" s="1"/>
+      <c r="F295" s="1"/>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>120</v>
       </c>
@@ -7650,8 +8260,10 @@
       <c r="D296" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E296" s="1"/>
+      <c r="F296" s="1"/>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>209</v>
       </c>
@@ -7664,8 +8276,10 @@
       <c r="D297" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E297" s="1"/>
+      <c r="F297" s="1"/>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>209</v>
       </c>
@@ -7678,8 +8292,10 @@
       <c r="D298" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E298" s="1"/>
+      <c r="F298" s="1"/>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>209</v>
       </c>
@@ -7692,8 +8308,10 @@
       <c r="D299" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E299" s="1"/>
+      <c r="F299" s="1"/>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>181</v>
       </c>
@@ -7706,8 +8324,10 @@
       <c r="D300" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E300" s="1"/>
+      <c r="F300" s="1"/>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>181</v>
       </c>
@@ -7720,8 +8340,10 @@
       <c r="D301" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E301" s="1"/>
+      <c r="F301" s="1"/>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>181</v>
       </c>
@@ -7734,8 +8356,10 @@
       <c r="D302" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E302" s="1"/>
+      <c r="F302" s="1"/>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>181</v>
       </c>
@@ -7748,8 +8372,10 @@
       <c r="D303" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E303" s="1"/>
+      <c r="F303" s="1"/>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>181</v>
       </c>
@@ -7762,8 +8388,10 @@
       <c r="D304" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E304" s="1"/>
+      <c r="F304" s="1"/>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>578</v>
       </c>
@@ -7776,8 +8404,10 @@
       <c r="D305" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E305" s="1"/>
+      <c r="F305" s="1"/>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>213</v>
       </c>
@@ -7790,8 +8420,10 @@
       <c r="D306" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E306" s="1"/>
+      <c r="F306" s="1"/>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>213</v>
       </c>
@@ -7804,8 +8436,10 @@
       <c r="D307" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E307" s="1"/>
+      <c r="F307" s="1"/>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>152</v>
       </c>
@@ -7818,8 +8452,10 @@
       <c r="D308" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E308" s="1"/>
+      <c r="F308" s="1"/>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>152</v>
       </c>
@@ -7832,8 +8468,10 @@
       <c r="D309" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E309" s="1"/>
+      <c r="F309" s="1"/>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>152</v>
       </c>
@@ -7846,8 +8484,10 @@
       <c r="D310" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E310" s="1"/>
+      <c r="F310" s="1"/>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>152</v>
       </c>
@@ -7860,8 +8500,10 @@
       <c r="D311" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E311" s="1"/>
+      <c r="F311" s="1"/>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>152</v>
       </c>
@@ -7874,8 +8516,10 @@
       <c r="D312" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E312" s="1"/>
+      <c r="F312" s="1"/>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>152</v>
       </c>
@@ -7888,8 +8532,10 @@
       <c r="D313" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E313" s="1"/>
+      <c r="F313" s="1"/>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>152</v>
       </c>
@@ -7902,8 +8548,10 @@
       <c r="D314" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E314" s="1"/>
+      <c r="F314" s="1"/>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>152</v>
       </c>
@@ -7916,8 +8564,10 @@
       <c r="D315" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E315" s="1"/>
+      <c r="F315" s="1"/>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>264</v>
       </c>
@@ -7930,8 +8580,10 @@
       <c r="D316" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E316" s="1"/>
+      <c r="F316" s="1"/>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>63</v>
       </c>
@@ -7944,8 +8596,10 @@
       <c r="D317" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E317" s="1"/>
+      <c r="F317" s="1"/>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>63</v>
       </c>
@@ -7958,8 +8612,10 @@
       <c r="D318" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E318" s="1"/>
+      <c r="F318" s="1"/>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>63</v>
       </c>
@@ -7972,8 +8628,10 @@
       <c r="D319" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E319" s="1"/>
+      <c r="F319" s="1"/>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>63</v>
       </c>
@@ -7986,8 +8644,10 @@
       <c r="D320" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E320" s="1"/>
+      <c r="F320" s="1"/>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>63</v>
       </c>
@@ -8000,8 +8660,10 @@
       <c r="D321" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E321" s="1"/>
+      <c r="F321" s="1"/>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>63</v>
       </c>
@@ -8014,8 +8676,10 @@
       <c r="D322" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E322" s="1"/>
+      <c r="F322" s="1"/>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>63</v>
       </c>
@@ -8028,8 +8692,10 @@
       <c r="D323" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E323" s="1"/>
+      <c r="F323" s="1"/>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>63</v>
       </c>
@@ -8042,8 +8708,10 @@
       <c r="D324" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E324" s="1"/>
+      <c r="F324" s="1"/>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>63</v>
       </c>
@@ -8056,8 +8724,10 @@
       <c r="D325" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E325" s="1"/>
+      <c r="F325" s="1"/>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>63</v>
       </c>
@@ -8070,8 +8740,10 @@
       <c r="D326" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E326" s="1"/>
+      <c r="F326" s="1"/>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>63</v>
       </c>
@@ -8084,8 +8756,10 @@
       <c r="D327" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E327" s="1"/>
+      <c r="F327" s="1"/>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>63</v>
       </c>
@@ -8098,8 +8772,10 @@
       <c r="D328" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E328" s="1"/>
+      <c r="F328" s="1"/>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>63</v>
       </c>
@@ -8112,8 +8788,10 @@
       <c r="D329" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E329" s="1"/>
+      <c r="F329" s="1"/>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>63</v>
       </c>
@@ -8126,8 +8804,10 @@
       <c r="D330" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E330" s="1"/>
+      <c r="F330" s="1"/>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>63</v>
       </c>
@@ -8140,8 +8820,10 @@
       <c r="D331" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E331" s="1"/>
+      <c r="F331" s="1"/>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>63</v>
       </c>
@@ -8154,8 +8836,10 @@
       <c r="D332" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E332" s="1"/>
+      <c r="F332" s="1"/>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>63</v>
       </c>
@@ -8168,8 +8852,10 @@
       <c r="D333" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E333" s="1"/>
+      <c r="F333" s="1"/>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>63</v>
       </c>
@@ -8182,8 +8868,10 @@
       <c r="D334" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E334" s="1"/>
+      <c r="F334" s="1"/>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>63</v>
       </c>
@@ -8196,8 +8884,10 @@
       <c r="D335" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E335" s="1"/>
+      <c r="F335" s="1"/>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>63</v>
       </c>
@@ -8210,8 +8900,10 @@
       <c r="D336" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E336" s="1"/>
+      <c r="F336" s="1"/>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>63</v>
       </c>
@@ -8224,8 +8916,10 @@
       <c r="D337" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E337" s="1"/>
+      <c r="F337" s="1"/>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>63</v>
       </c>
@@ -8238,8 +8932,10 @@
       <c r="D338" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E338" s="1"/>
+      <c r="F338" s="1"/>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>63</v>
       </c>
@@ -8252,8 +8948,10 @@
       <c r="D339" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E339" s="1"/>
+      <c r="F339" s="1"/>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>63</v>
       </c>
@@ -8266,8 +8964,10 @@
       <c r="D340" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E340" s="1"/>
+      <c r="F340" s="1"/>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>63</v>
       </c>
@@ -8280,8 +8980,10 @@
       <c r="D341" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E341" s="1"/>
+      <c r="F341" s="1"/>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>63</v>
       </c>
@@ -8294,8 +8996,10 @@
       <c r="D342" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E342" s="1"/>
+      <c r="F342" s="1"/>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>63</v>
       </c>
@@ -8308,8 +9012,10 @@
       <c r="D343" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E343" s="1"/>
+      <c r="F343" s="1"/>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>63</v>
       </c>
@@ -8322,8 +9028,10 @@
       <c r="D344" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E344" s="1"/>
+      <c r="F344" s="1"/>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>63</v>
       </c>
@@ -8336,8 +9044,10 @@
       <c r="D345" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E345" s="1"/>
+      <c r="F345" s="1"/>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>63</v>
       </c>
@@ -8350,8 +9060,10 @@
       <c r="D346" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E346" s="1"/>
+      <c r="F346" s="1"/>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>63</v>
       </c>
@@ -8364,8 +9076,10 @@
       <c r="D347" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E347" s="1"/>
+      <c r="F347" s="1"/>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>63</v>
       </c>
@@ -8378,8 +9092,10 @@
       <c r="D348" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E348" s="1"/>
+      <c r="F348" s="1"/>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>63</v>
       </c>
@@ -8392,8 +9108,10 @@
       <c r="D349" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E349" s="1"/>
+      <c r="F349" s="1"/>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>63</v>
       </c>
@@ -8406,8 +9124,10 @@
       <c r="D350" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E350" s="1"/>
+      <c r="F350" s="1"/>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>63</v>
       </c>
@@ -8420,8 +9140,10 @@
       <c r="D351" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E351" s="1"/>
+      <c r="F351" s="1"/>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>63</v>
       </c>
@@ -8434,8 +9156,10 @@
       <c r="D352" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E352" s="1"/>
+      <c r="F352" s="1"/>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>63</v>
       </c>
@@ -8448,8 +9172,10 @@
       <c r="D353" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E353" s="1"/>
+      <c r="F353" s="1"/>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>63</v>
       </c>
@@ -8462,8 +9188,10 @@
       <c r="D354" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E354" s="1"/>
+      <c r="F354" s="1"/>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>63</v>
       </c>
@@ -8476,8 +9204,10 @@
       <c r="D355" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E355" s="1"/>
+      <c r="F355" s="1"/>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>63</v>
       </c>
@@ -8490,8 +9220,10 @@
       <c r="D356" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E356" s="1"/>
+      <c r="F356" s="1"/>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>63</v>
       </c>
@@ -8504,8 +9236,10 @@
       <c r="D357" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E357" s="1"/>
+      <c r="F357" s="1"/>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>63</v>
       </c>
@@ -8518,8 +9252,10 @@
       <c r="D358" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E358" s="1"/>
+      <c r="F358" s="1"/>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>418</v>
       </c>
@@ -8532,8 +9268,10 @@
       <c r="D359" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E359" s="1"/>
+      <c r="F359" s="1"/>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>357</v>
       </c>
@@ -8546,8 +9284,10 @@
       <c r="D360" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E360" s="1"/>
+      <c r="F360" s="1"/>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>357</v>
       </c>
@@ -8560,8 +9300,10 @@
       <c r="D361" s="1" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E361" s="1"/>
+      <c r="F361" s="1"/>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>170</v>
       </c>
@@ -8574,8 +9316,10 @@
       <c r="D362" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E362" s="1"/>
+      <c r="F362" s="1"/>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>305</v>
       </c>
@@ -8588,8 +9332,10 @@
       <c r="D363" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E363" s="1"/>
+      <c r="F363" s="1"/>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>305</v>
       </c>
@@ -8602,8 +9348,10 @@
       <c r="D364" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E364" s="1"/>
+      <c r="F364" s="1"/>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>233</v>
       </c>
@@ -8616,8 +9364,10 @@
       <c r="D365" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E365" s="1"/>
+      <c r="F365" s="1"/>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>347</v>
       </c>
@@ -8630,8 +9380,10 @@
       <c r="D366" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E366" s="1"/>
+      <c r="F366" s="1"/>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>291</v>
       </c>
@@ -8644,8 +9396,10 @@
       <c r="D367" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E367" s="1"/>
+      <c r="F367" s="1"/>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>200</v>
       </c>
@@ -8658,8 +9412,10 @@
       <c r="D368" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E368" s="1"/>
+      <c r="F368" s="1"/>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>286</v>
       </c>
@@ -8672,8 +9428,10 @@
       <c r="D369" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E369" s="1"/>
+      <c r="F369" s="1"/>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>321</v>
       </c>
@@ -8686,8 +9444,10 @@
       <c r="D370" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E370" s="1"/>
+      <c r="F370" s="1"/>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>444</v>
       </c>
@@ -8700,8 +9460,10 @@
       <c r="D371" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E371" s="1"/>
+      <c r="F371" s="1"/>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>155</v>
       </c>
@@ -8714,8 +9476,10 @@
       <c r="D372" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E372" s="1"/>
+      <c r="F372" s="1"/>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>235</v>
       </c>
@@ -8728,8 +9492,10 @@
       <c r="D373" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E373" s="1"/>
+      <c r="F373" s="1"/>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>129</v>
       </c>
@@ -8742,8 +9508,10 @@
       <c r="D374" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E374" s="1"/>
+      <c r="F374" s="1"/>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>129</v>
       </c>
@@ -8756,8 +9524,10 @@
       <c r="D375" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E375" s="1"/>
+      <c r="F375" s="1"/>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>189</v>
       </c>
@@ -8770,8 +9540,10 @@
       <c r="D376" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E376" s="1"/>
+      <c r="F376" s="1"/>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>189</v>
       </c>
@@ -8784,8 +9556,10 @@
       <c r="D377" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E377" s="1"/>
+      <c r="F377" s="1"/>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>260</v>
       </c>
@@ -8798,8 +9572,10 @@
       <c r="D378" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E378" s="1"/>
+      <c r="F378" s="1"/>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>307</v>
       </c>
@@ -8812,8 +9588,10 @@
       <c r="D379" s="1" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E379" s="1"/>
+      <c r="F379" s="1"/>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>518</v>
       </c>
@@ -8826,8 +9604,10 @@
       <c r="D380" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E380" s="1"/>
+      <c r="F380" s="1"/>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>191</v>
       </c>
@@ -8840,8 +9620,10 @@
       <c r="D381" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E381" s="1"/>
+      <c r="F381" s="1"/>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>258</v>
       </c>
@@ -8854,8 +9636,10 @@
       <c r="D382" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E382" s="1"/>
+      <c r="F382" s="1"/>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>569</v>
       </c>
@@ -8868,8 +9652,10 @@
       <c r="D383" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E383" s="1"/>
+      <c r="F383" s="1"/>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>513</v>
       </c>
@@ -8882,8 +9668,10 @@
       <c r="D384" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E384" s="1"/>
+      <c r="F384" s="1"/>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>242</v>
       </c>
@@ -8896,8 +9684,10 @@
       <c r="D385" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E385" s="1"/>
+      <c r="F385" s="1"/>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>252</v>
       </c>
@@ -8910,8 +9700,10 @@
       <c r="D386" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E386" s="1"/>
+      <c r="F386" s="1"/>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>34</v>
       </c>
@@ -8924,8 +9716,10 @@
       <c r="D387" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E387" s="1"/>
+      <c r="F387" s="1"/>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>34</v>
       </c>
@@ -8938,8 +9732,10 @@
       <c r="D388" s="1" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E388" s="1"/>
+      <c r="F388" s="1"/>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>34</v>
       </c>
@@ -8952,8 +9748,10 @@
       <c r="D389" s="1" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E389" s="1"/>
+      <c r="F389" s="1"/>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>34</v>
       </c>
@@ -8966,8 +9764,10 @@
       <c r="D390" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E390" s="1"/>
+      <c r="F390" s="1"/>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>521</v>
       </c>
@@ -8980,8 +9780,10 @@
       <c r="D391" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E391" s="1"/>
+      <c r="F391" s="1"/>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>570</v>
       </c>
@@ -8994,8 +9796,10 @@
       <c r="D392" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E392" s="1"/>
+      <c r="F392" s="1"/>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>350</v>
       </c>
@@ -9008,8 +9812,10 @@
       <c r="D393" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E393" s="1"/>
+      <c r="F393" s="1"/>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>350</v>
       </c>
@@ -9022,8 +9828,10 @@
       <c r="D394" s="1" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E394" s="1"/>
+      <c r="F394" s="1"/>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>350</v>
       </c>
@@ -9036,8 +9844,10 @@
       <c r="D395" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E395" s="1"/>
+      <c r="F395" s="1"/>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>350</v>
       </c>
@@ -9050,8 +9860,10 @@
       <c r="D396" s="1" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E396" s="1"/>
+      <c r="F396" s="1"/>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>350</v>
       </c>
@@ -9064,8 +9876,10 @@
       <c r="D397" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E397" s="1"/>
+      <c r="F397" s="1"/>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>350</v>
       </c>
@@ -9078,8 +9892,10 @@
       <c r="D398" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E398" s="1"/>
+      <c r="F398" s="1"/>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>18</v>
       </c>
@@ -9092,8 +9908,10 @@
       <c r="D399" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E399" s="1"/>
+      <c r="F399" s="1"/>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>18</v>
       </c>
@@ -9106,8 +9924,10 @@
       <c r="D400" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E400" s="1"/>
+      <c r="F400" s="1"/>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>18</v>
       </c>
@@ -9120,8 +9940,10 @@
       <c r="D401" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E401" s="1"/>
+      <c r="F401" s="1"/>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>18</v>
       </c>
@@ -9134,8 +9956,10 @@
       <c r="D402" s="1" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E402" s="1"/>
+      <c r="F402" s="1"/>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>18</v>
       </c>
@@ -9148,8 +9972,10 @@
       <c r="D403" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E403" s="1"/>
+      <c r="F403" s="1"/>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>18</v>
       </c>
@@ -9162,8 +9988,10 @@
       <c r="D404" s="1" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E404" s="1"/>
+      <c r="F404" s="1"/>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>18</v>
       </c>
@@ -9176,8 +10004,10 @@
       <c r="D405" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E405" s="1"/>
+      <c r="F405" s="1"/>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>18</v>
       </c>
@@ -9190,8 +10020,10 @@
       <c r="D406" s="1" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E406" s="1"/>
+      <c r="F406" s="1"/>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>18</v>
       </c>
@@ -9204,8 +10036,10 @@
       <c r="D407" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E407" s="1"/>
+      <c r="F407" s="1"/>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>18</v>
       </c>
@@ -9218,8 +10052,10 @@
       <c r="D408" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E408" s="1"/>
+      <c r="F408" s="1"/>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>18</v>
       </c>
@@ -9232,8 +10068,10 @@
       <c r="D409" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E409" s="1"/>
+      <c r="F409" s="1"/>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>18</v>
       </c>
@@ -9246,8 +10084,10 @@
       <c r="D410" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E410" s="1"/>
+      <c r="F410" s="1"/>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>18</v>
       </c>
@@ -9260,8 +10100,10 @@
       <c r="D411" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E411" s="1"/>
+      <c r="F411" s="1"/>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>18</v>
       </c>
@@ -9274,8 +10116,10 @@
       <c r="D412" s="1" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E412" s="1"/>
+      <c r="F412" s="1"/>
+    </row>
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>18</v>
       </c>
@@ -9288,8 +10132,10 @@
       <c r="D413" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E413" s="1"/>
+      <c r="F413" s="1"/>
+    </row>
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>18</v>
       </c>
@@ -9302,8 +10148,10 @@
       <c r="D414" s="1" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E414" s="1"/>
+      <c r="F414" s="1"/>
+    </row>
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>18</v>
       </c>
@@ -9316,8 +10164,10 @@
       <c r="D415" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E415" s="1"/>
+      <c r="F415" s="1"/>
+    </row>
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>18</v>
       </c>
@@ -9330,8 +10180,10 @@
       <c r="D416" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E416" s="1"/>
+      <c r="F416" s="1"/>
+    </row>
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>18</v>
       </c>
@@ -9344,8 +10196,10 @@
       <c r="D417" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E417" s="1"/>
+      <c r="F417" s="1"/>
+    </row>
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>18</v>
       </c>
@@ -9358,8 +10212,10 @@
       <c r="D418" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E418" s="1"/>
+      <c r="F418" s="1"/>
+    </row>
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>230</v>
       </c>
@@ -9372,8 +10228,10 @@
       <c r="D419" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E419" s="1"/>
+      <c r="F419" s="1"/>
+    </row>
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>131</v>
       </c>
@@ -9386,8 +10244,10 @@
       <c r="D420" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E420" s="1"/>
+      <c r="F420" s="1"/>
+    </row>
+    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>131</v>
       </c>
@@ -9400,8 +10260,10 @@
       <c r="D421" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E421" s="1"/>
+      <c r="F421" s="1"/>
+    </row>
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>53</v>
       </c>
@@ -9414,8 +10276,10 @@
       <c r="D422" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E422" s="1"/>
+      <c r="F422" s="1"/>
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>53</v>
       </c>
@@ -9428,8 +10292,10 @@
       <c r="D423" s="1" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E423" s="1"/>
+      <c r="F423" s="1"/>
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>159</v>
       </c>
@@ -9442,8 +10308,10 @@
       <c r="D424" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E424" s="1"/>
+      <c r="F424" s="1"/>
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>159</v>
       </c>
@@ -9456,8 +10324,10 @@
       <c r="D425" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E425" s="1"/>
+      <c r="F425" s="1"/>
+    </row>
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>21</v>
       </c>
@@ -9470,8 +10340,10 @@
       <c r="D426" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E426" s="1"/>
+      <c r="F426" s="1"/>
+    </row>
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>21</v>
       </c>
@@ -9484,8 +10356,10 @@
       <c r="D427" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E427" s="1"/>
+      <c r="F427" s="1"/>
+    </row>
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>21</v>
       </c>
@@ -9498,8 +10372,10 @@
       <c r="D428" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E428" s="1"/>
+      <c r="F428" s="1"/>
+    </row>
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>21</v>
       </c>
@@ -9512,8 +10388,10 @@
       <c r="D429" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E429" s="1"/>
+      <c r="F429" s="1"/>
+    </row>
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>21</v>
       </c>
@@ -9526,8 +10404,10 @@
       <c r="D430" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E430" s="1"/>
+      <c r="F430" s="1"/>
+    </row>
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>21</v>
       </c>
@@ -9540,8 +10420,10 @@
       <c r="D431" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E431" s="1"/>
+      <c r="F431" s="1"/>
+    </row>
+    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>21</v>
       </c>
@@ -9554,8 +10436,10 @@
       <c r="D432" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E432" s="1"/>
+      <c r="F432" s="1"/>
+    </row>
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>21</v>
       </c>
@@ -9568,8 +10452,10 @@
       <c r="D433" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E433" s="1"/>
+      <c r="F433" s="1"/>
+    </row>
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>21</v>
       </c>
@@ -9582,8 +10468,10 @@
       <c r="D434" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E434" s="1"/>
+      <c r="F434" s="1"/>
+    </row>
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>21</v>
       </c>
@@ -9596,8 +10484,10 @@
       <c r="D435" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E435" s="1"/>
+      <c r="F435" s="1"/>
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>32</v>
       </c>
@@ -9610,8 +10500,10 @@
       <c r="D436" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E436" s="1"/>
+      <c r="F436" s="1"/>
+    </row>
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>32</v>
       </c>
@@ -9624,8 +10516,10 @@
       <c r="D437" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E437" s="1"/>
+      <c r="F437" s="1"/>
+    </row>
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>32</v>
       </c>
@@ -9638,8 +10532,10 @@
       <c r="D438" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E438" s="1"/>
+      <c r="F438" s="1"/>
+    </row>
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>32</v>
       </c>
@@ -9652,8 +10548,10 @@
       <c r="D439" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E439" s="1"/>
+      <c r="F439" s="1"/>
+    </row>
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>32</v>
       </c>
@@ -9666,8 +10564,10 @@
       <c r="D440" s="1" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E440" s="1"/>
+      <c r="F440" s="1"/>
+    </row>
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>32</v>
       </c>
@@ -9680,8 +10580,10 @@
       <c r="D441" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E441" s="1"/>
+      <c r="F441" s="1"/>
+    </row>
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>32</v>
       </c>
@@ -9694,8 +10596,10 @@
       <c r="D442" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E442" s="1"/>
+      <c r="F442" s="1"/>
+    </row>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>32</v>
       </c>
@@ -9708,8 +10612,10 @@
       <c r="D443" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E443" s="1"/>
+      <c r="F443" s="1"/>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>254</v>
       </c>
@@ -9722,8 +10628,10 @@
       <c r="D444" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E444" s="1"/>
+      <c r="F444" s="1"/>
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>254</v>
       </c>
@@ -9736,8 +10644,10 @@
       <c r="D445" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E445" s="1"/>
+      <c r="F445" s="1"/>
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>541</v>
       </c>
@@ -9750,8 +10660,10 @@
       <c r="D446" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E446" s="1"/>
+      <c r="F446" s="1"/>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>266</v>
       </c>
@@ -9764,8 +10676,10 @@
       <c r="D447" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E447" s="1"/>
+      <c r="F447" s="1"/>
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>359</v>
       </c>
@@ -9778,8 +10692,10 @@
       <c r="D448" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E448" s="1"/>
+      <c r="F448" s="1"/>
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>48</v>
       </c>
@@ -9792,8 +10708,10 @@
       <c r="D449" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E449" s="1"/>
+      <c r="F449" s="1"/>
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>48</v>
       </c>
@@ -9806,8 +10724,10 @@
       <c r="D450" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E450" s="1"/>
+      <c r="F450" s="1"/>
+    </row>
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>48</v>
       </c>
@@ -9820,8 +10740,10 @@
       <c r="D451" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E451" s="1"/>
+      <c r="F451" s="1"/>
+    </row>
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>48</v>
       </c>
@@ -9834,8 +10756,10 @@
       <c r="D452" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E452" s="1"/>
+      <c r="F452" s="1"/>
+    </row>
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>48</v>
       </c>
@@ -9848,8 +10772,10 @@
       <c r="D453" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E453" s="1"/>
+      <c r="F453" s="1"/>
+    </row>
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>48</v>
       </c>
@@ -9862,8 +10788,10 @@
       <c r="D454" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E454" s="1"/>
+      <c r="F454" s="1"/>
+    </row>
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>48</v>
       </c>
@@ -9876,8 +10804,10 @@
       <c r="D455" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E455" s="1"/>
+      <c r="F455" s="1"/>
+    </row>
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>48</v>
       </c>
@@ -9890,8 +10820,10 @@
       <c r="D456" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E456" s="1"/>
+      <c r="F456" s="1"/>
+    </row>
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>48</v>
       </c>
@@ -9904,8 +10836,10 @@
       <c r="D457" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E457" s="1"/>
+      <c r="F457" s="1"/>
+    </row>
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>48</v>
       </c>
@@ -9918,8 +10852,10 @@
       <c r="D458" s="1" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E458" s="1"/>
+      <c r="F458" s="1"/>
+    </row>
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>48</v>
       </c>
@@ -9932,8 +10868,10 @@
       <c r="D459" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E459" s="1"/>
+      <c r="F459" s="1"/>
+    </row>
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>48</v>
       </c>
@@ -9946,8 +10884,10 @@
       <c r="D460" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E460" s="1"/>
+      <c r="F460" s="1"/>
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>48</v>
       </c>
@@ -9960,8 +10900,10 @@
       <c r="D461" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E461" s="1"/>
+      <c r="F461" s="1"/>
+    </row>
+    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>48</v>
       </c>
@@ -9974,8 +10916,10 @@
       <c r="D462" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E462" s="1"/>
+      <c r="F462" s="1"/>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>48</v>
       </c>
@@ -9988,8 +10932,10 @@
       <c r="D463" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E463" s="1"/>
+      <c r="F463" s="1"/>
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>473</v>
       </c>
@@ -10002,8 +10948,10 @@
       <c r="D464" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E464" s="1"/>
+      <c r="F464" s="1"/>
+    </row>
+    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>277</v>
       </c>
@@ -10016,8 +10964,10 @@
       <c r="D465" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E465" s="1"/>
+      <c r="F465" s="1"/>
+    </row>
+    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>537</v>
       </c>
@@ -10030,8 +10980,10 @@
       <c r="D466" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E466" s="1"/>
+      <c r="F466" s="1"/>
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>370</v>
       </c>
@@ -10044,8 +10996,10 @@
       <c r="D467" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E467" s="1"/>
+      <c r="F467" s="1"/>
+    </row>
+    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>480</v>
       </c>
@@ -10058,8 +11012,10 @@
       <c r="D468" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E468" s="1"/>
+      <c r="F468" s="1"/>
+    </row>
+    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>480</v>
       </c>
@@ -10072,8 +11028,10 @@
       <c r="D469" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E469" s="1"/>
+      <c r="F469" s="1"/>
+    </row>
+    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>471</v>
       </c>
@@ -10086,8 +11044,10 @@
       <c r="D470" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E470" s="1"/>
+      <c r="F470" s="1"/>
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>471</v>
       </c>
@@ -10100,8 +11060,10 @@
       <c r="D471" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E471" s="1"/>
+      <c r="F471" s="1"/>
+    </row>
+    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>471</v>
       </c>
@@ -10114,8 +11076,10 @@
       <c r="D472" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E472" s="1"/>
+      <c r="F472" s="1"/>
+    </row>
+    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>471</v>
       </c>
@@ -10128,8 +11092,10 @@
       <c r="D473" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E473" s="1"/>
+      <c r="F473" s="1"/>
+    </row>
+    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>36</v>
       </c>
@@ -10142,8 +11108,10 @@
       <c r="D474" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E474" s="1"/>
+      <c r="F474" s="1"/>
+    </row>
+    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>36</v>
       </c>
@@ -10156,8 +11124,10 @@
       <c r="D475" s="1" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E475" s="1"/>
+      <c r="F475" s="1"/>
+    </row>
+    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>36</v>
       </c>
@@ -10170,8 +11140,10 @@
       <c r="D476" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E476" s="1"/>
+      <c r="F476" s="1"/>
+    </row>
+    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>36</v>
       </c>
@@ -10184,8 +11156,10 @@
       <c r="D477" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E477" s="1"/>
+      <c r="F477" s="1"/>
+    </row>
+    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>36</v>
       </c>
@@ -10198,8 +11172,10 @@
       <c r="D478" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E478" s="1"/>
+      <c r="F478" s="1"/>
+    </row>
+    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>539</v>
       </c>
@@ -10212,8 +11188,10 @@
       <c r="D479" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E479" s="1"/>
+      <c r="F479" s="1"/>
+    </row>
+    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>316</v>
       </c>
@@ -10226,8 +11204,10 @@
       <c r="D480" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E480" s="1"/>
+      <c r="F480" s="1"/>
+    </row>
+    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>316</v>
       </c>
@@ -10240,8 +11220,10 @@
       <c r="D481" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E481" s="1"/>
+      <c r="F481" s="1"/>
+    </row>
+    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>361</v>
       </c>
@@ -10254,8 +11236,10 @@
       <c r="D482" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E482" s="1"/>
+      <c r="F482" s="1"/>
+    </row>
+    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>530</v>
       </c>
@@ -10268,8 +11252,10 @@
       <c r="D483" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E483" s="1"/>
+      <c r="F483" s="1"/>
+    </row>
+    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>256</v>
       </c>
@@ -10282,8 +11268,10 @@
       <c r="D484" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E484" s="1"/>
+      <c r="F484" s="1"/>
+    </row>
+    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>423</v>
       </c>
@@ -10296,8 +11284,10 @@
       <c r="D485" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E485" s="1"/>
+      <c r="F485" s="1"/>
+    </row>
+    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>135</v>
       </c>
@@ -10310,8 +11300,10 @@
       <c r="D486" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E486" s="1"/>
+      <c r="F486" s="1"/>
+    </row>
+    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>135</v>
       </c>
@@ -10324,8 +11316,10 @@
       <c r="D487" s="1" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E487" s="1"/>
+      <c r="F487" s="1"/>
+    </row>
+    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>135</v>
       </c>
@@ -10338,8 +11332,10 @@
       <c r="D488" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E488" s="1"/>
+      <c r="F488" s="1"/>
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>450</v>
       </c>
@@ -10352,8 +11348,10 @@
       <c r="D489" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E489" s="1"/>
+      <c r="F489" s="1"/>
+    </row>
+    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>450</v>
       </c>
@@ -10366,8 +11364,10 @@
       <c r="D490" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E490" s="1"/>
+      <c r="F490" s="1"/>
+    </row>
+    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>450</v>
       </c>
@@ -10380,8 +11380,10 @@
       <c r="D491" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E491" s="1"/>
+      <c r="F491" s="1"/>
+    </row>
+    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>262</v>
       </c>
@@ -10394,8 +11396,10 @@
       <c r="D492" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E492" s="1"/>
+      <c r="F492" s="1"/>
+    </row>
+    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>262</v>
       </c>
@@ -10408,8 +11412,10 @@
       <c r="D493" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E493" s="1"/>
+      <c r="F493" s="1"/>
+    </row>
+    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>142</v>
       </c>
@@ -10422,8 +11428,10 @@
       <c r="D494" s="1" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E494" s="1"/>
+      <c r="F494" s="1"/>
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>142</v>
       </c>
@@ -10436,8 +11444,10 @@
       <c r="D495" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E495" s="1"/>
+      <c r="F495" s="1"/>
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>142</v>
       </c>
@@ -10450,8 +11460,10 @@
       <c r="D496" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E496" s="1"/>
+      <c r="F496" s="1"/>
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>551</v>
       </c>
@@ -10464,8 +11476,10 @@
       <c r="D497" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E497" s="1"/>
+      <c r="F497" s="1"/>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>504</v>
       </c>
@@ -10478,8 +11492,10 @@
       <c r="D498" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E498" s="1"/>
+      <c r="F498" s="1"/>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>562</v>
       </c>
@@ -10492,8 +11508,10 @@
       <c r="D499" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E499" s="1"/>
+      <c r="F499" s="1"/>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>362</v>
       </c>
@@ -10506,8 +11524,10 @@
       <c r="D500" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E500" s="1"/>
+      <c r="F500" s="1"/>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>362</v>
       </c>
@@ -10520,8 +11540,10 @@
       <c r="D501" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E501" s="1"/>
+      <c r="F501" s="1"/>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>475</v>
       </c>
@@ -10534,8 +11556,10 @@
       <c r="D502" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E502" s="1"/>
+      <c r="F502" s="1"/>
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>475</v>
       </c>
@@ -10548,8 +11572,10 @@
       <c r="D503" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E503" s="1"/>
+      <c r="F503" s="1"/>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>268</v>
       </c>
@@ -10562,8 +11588,10 @@
       <c r="D504" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E504" s="1"/>
+      <c r="F504" s="1"/>
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>268</v>
       </c>
@@ -10576,8 +11604,10 @@
       <c r="D505" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E505" s="1"/>
+      <c r="F505" s="1"/>
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>268</v>
       </c>
@@ -10590,8 +11620,10 @@
       <c r="D506" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E506" s="1"/>
+      <c r="F506" s="1"/>
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>506</v>
       </c>
@@ -10604,8 +11636,10 @@
       <c r="D507" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E507" s="1"/>
+      <c r="F507" s="1"/>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>506</v>
       </c>
@@ -10618,8 +11652,10 @@
       <c r="D508" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E508" s="1"/>
+      <c r="F508" s="1"/>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>137</v>
       </c>
@@ -10632,8 +11668,10 @@
       <c r="D509" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E509" s="1"/>
+      <c r="F509" s="1"/>
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>137</v>
       </c>
@@ -10646,8 +11684,10 @@
       <c r="D510" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E510" s="1"/>
+      <c r="F510" s="1"/>
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>490</v>
       </c>
@@ -10660,8 +11700,10 @@
       <c r="D511" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E511" s="1"/>
+      <c r="F511" s="1"/>
+    </row>
+    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>138</v>
       </c>
@@ -10674,8 +11716,10 @@
       <c r="D512" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E512" s="1"/>
+      <c r="F512" s="1"/>
+    </row>
+    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>138</v>
       </c>
@@ -10688,8 +11732,10 @@
       <c r="D513" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E513" s="1"/>
+      <c r="F513" s="1"/>
+    </row>
+    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>138</v>
       </c>
@@ -10702,8 +11748,10 @@
       <c r="D514" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E514" s="1"/>
+      <c r="F514" s="1"/>
+    </row>
+    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>138</v>
       </c>
@@ -10716,8 +11764,10 @@
       <c r="D515" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E515" s="1"/>
+      <c r="F515" s="1"/>
+    </row>
+    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>194</v>
       </c>
@@ -10730,8 +11780,10 @@
       <c r="D516" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E516" s="1"/>
+      <c r="F516" s="1"/>
+    </row>
+    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>194</v>
       </c>
@@ -10744,8 +11796,10 @@
       <c r="D517" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E517" s="1"/>
+      <c r="F517" s="1"/>
+    </row>
+    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>194</v>
       </c>
@@ -10758,8 +11812,10 @@
       <c r="D518" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E518" s="1"/>
+      <c r="F518" s="1"/>
+    </row>
+    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>194</v>
       </c>
@@ -10772,8 +11828,10 @@
       <c r="D519" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E519" s="1"/>
+      <c r="F519" s="1"/>
+    </row>
+    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>194</v>
       </c>
@@ -10786,8 +11844,10 @@
       <c r="D520" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E520" s="1"/>
+      <c r="F520" s="1"/>
+    </row>
+    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>194</v>
       </c>
@@ -10800,8 +11860,10 @@
       <c r="D521" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E521" s="1"/>
+      <c r="F521" s="1"/>
+    </row>
+    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>194</v>
       </c>
@@ -10814,8 +11876,10 @@
       <c r="D522" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E522" s="1"/>
+      <c r="F522" s="1"/>
+    </row>
+    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>194</v>
       </c>
@@ -10828,8 +11892,10 @@
       <c r="D523" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E523" s="1"/>
+      <c r="F523" s="1"/>
+    </row>
+    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>591</v>
       </c>
@@ -10842,8 +11908,10 @@
       <c r="D524" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E524" s="1"/>
+      <c r="F524" s="1"/>
+    </row>
+    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>50</v>
       </c>
@@ -10856,8 +11924,10 @@
       <c r="D525" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E525" s="1"/>
+      <c r="F525" s="1"/>
+    </row>
+    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>50</v>
       </c>
@@ -10870,8 +11940,10 @@
       <c r="D526" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E526" s="1"/>
+      <c r="F526" s="1"/>
+    </row>
+    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>50</v>
       </c>
@@ -10884,8 +11956,10 @@
       <c r="D527" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E527" s="1"/>
+      <c r="F527" s="1"/>
+    </row>
+    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>50</v>
       </c>
@@ -10898,8 +11972,10 @@
       <c r="D528" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E528" s="1"/>
+      <c r="F528" s="1"/>
+    </row>
+    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>50</v>
       </c>
@@ -10912,8 +11988,10 @@
       <c r="D529" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E529" s="1"/>
+      <c r="F529" s="1"/>
+    </row>
+    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>50</v>
       </c>
@@ -10926,8 +12004,10 @@
       <c r="D530" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E530" s="1"/>
+      <c r="F530" s="1"/>
+    </row>
+    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>501</v>
       </c>
@@ -10940,8 +12020,10 @@
       <c r="D531" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E531" s="1"/>
+      <c r="F531" s="1"/>
+    </row>
+    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>38</v>
       </c>
@@ -10954,8 +12036,10 @@
       <c r="D532" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E532" s="1"/>
+      <c r="F532" s="1"/>
+    </row>
+    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>38</v>
       </c>
@@ -10968,8 +12052,10 @@
       <c r="D533" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E533" s="1"/>
+      <c r="F533" s="1"/>
+    </row>
+    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>38</v>
       </c>
@@ -10982,8 +12068,10 @@
       <c r="D534" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E534" s="1"/>
+      <c r="F534" s="1"/>
+    </row>
+    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>38</v>
       </c>
@@ -10996,8 +12084,10 @@
       <c r="D535" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E535" s="1"/>
+      <c r="F535" s="1"/>
+    </row>
+    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>38</v>
       </c>
@@ -11010,8 +12100,10 @@
       <c r="D536" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E536" s="1"/>
+      <c r="F536" s="1"/>
+    </row>
+    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>38</v>
       </c>
@@ -11024,8 +12116,10 @@
       <c r="D537" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E537" s="1"/>
+      <c r="F537" s="1"/>
+    </row>
+    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>38</v>
       </c>
@@ -11038,8 +12132,10 @@
       <c r="D538" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E538" s="1"/>
+      <c r="F538" s="1"/>
+    </row>
+    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>38</v>
       </c>
@@ -11052,8 +12148,10 @@
       <c r="D539" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E539" s="1"/>
+      <c r="F539" s="1"/>
+    </row>
+    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>38</v>
       </c>
@@ -11066,8 +12164,10 @@
       <c r="D540" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E540" s="1"/>
+      <c r="F540" s="1"/>
+    </row>
+    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>82</v>
       </c>
@@ -11080,8 +12180,10 @@
       <c r="D541" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E541" s="1"/>
+      <c r="F541" s="1"/>
+    </row>
+    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>82</v>
       </c>
@@ -11094,8 +12196,10 @@
       <c r="D542" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E542" s="1"/>
+      <c r="F542" s="1"/>
+    </row>
+    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>451</v>
       </c>
@@ -11108,8 +12212,10 @@
       <c r="D543" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E543" s="1"/>
+      <c r="F543" s="1"/>
+    </row>
+    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>461</v>
       </c>
@@ -11122,8 +12228,10 @@
       <c r="D544" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E544" s="1"/>
+      <c r="F544" s="1"/>
+    </row>
+    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>10</v>
       </c>
@@ -11136,8 +12244,10 @@
       <c r="D545" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E545" s="1"/>
+      <c r="F545" s="1"/>
+    </row>
+    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>468</v>
       </c>
@@ -11150,8 +12260,10 @@
       <c r="D546" s="1" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E546" s="1"/>
+      <c r="F546" s="1"/>
+    </row>
+    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>468</v>
       </c>
@@ -11164,8 +12276,10 @@
       <c r="D547" s="1" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E547" s="1"/>
+      <c r="F547" s="1"/>
+    </row>
+    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>250</v>
       </c>
@@ -11178,6 +12292,8 @@
       <c r="D548" s="1" t="s">
         <v>164</v>
       </c>
+      <c r="E548" s="1"/>
+      <c r="F548" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
